--- a/output/pdf_financials_xlsx/VKG.xlsx
+++ b/output/pdf_financials_xlsx/VKG.xlsx
@@ -4543,40 +4543,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.477742</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.491408</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.491408</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.512844</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.578522</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.578522</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.578522</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.471896</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.499396</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.499396</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.499396</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.499396</v>
       </c>
     </row>
     <row r="93">
@@ -7032,7 +7032,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -7790,7 +7794,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -8092,7 +8100,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -9014,7 +9026,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.477742</v>
       </c>

--- a/output/pdf_financials_xlsx/VKG.xlsx
+++ b/output/pdf_financials_xlsx/VKG.xlsx
@@ -1909,40 +1909,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000278</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.021857</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000118</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.01744</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.022644</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.019197</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002228</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.002834</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003083</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.002321</v>
       </c>
     </row>
     <row r="35">
@@ -1995,40 +1995,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.004</v>
+        <v>0.004278</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.021857</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000118</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.01744</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.022644</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.019197</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002228</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.002834</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003083</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.002321</v>
       </c>
     </row>
     <row r="37">
@@ -2511,40 +2511,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.00222</v>
+        <v>0.001942</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.001942</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.023799</v>
+        <v>0.001942</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.00206</v>
+        <v>0.001942</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.019382</v>
+        <v>0.001942</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.024586</v>
+        <v>0.001942</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.7e-05</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.02051</v>
+        <v>0.001313</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002228</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.002834</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.003083</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.002321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/VKG.xlsx
+++ b/output/pdf_financials_xlsx/VKG.xlsx
@@ -11246,7 +11246,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
